--- a/56/food/tm2026-sm.xlsx
+++ b/56/food/tm2026-sm.xlsx
@@ -1127,7 +1127,7 @@
       </c>
       <c r="H2" s="57" t="inlineStr">
         <is>
-          <t>Ойбуев И.Н.</t>
+          <t>Ойбуев Ибрагим Нуридович</t>
         </is>
       </c>
       <c r="I2" s="58" t="n"/>
